--- a/General_utils/surveyCodeBook.xlsx
+++ b/General_utils/surveyCodeBook.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jproctor\Dropbox\Research\Projects\SmallAreaEstimationForSurveyIndicators\RawData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bmgf-my.sharepoint.com/personal/jeremy_cooper_gatesfoundation_org/Documents/Documents/GitHub/SmallAreaEstimationForSurveyIndicators - Docker Test/General_utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7375EEDF-9E24-48B1-A3E8-B92F4507930D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7375EEDF-9E24-48B1-A3E8-B92F4507930D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F0CD255-48D2-4790-B632-C5FCDBDE88D9}"/>
   <bookViews>
-    <workbookView xWindow="2650" yWindow="1230" windowWidth="14400" windowHeight="7360" xr2:uid="{03C38CC3-CE66-45D3-8C15-AF54B36715CE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{03C38CC3-CE66-45D3-8C15-AF54B36715CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$102</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1395,7 +1395,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1430,9 +1430,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1451,9 +1450,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1491,7 +1490,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1597,7 +1596,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1739,7 +1738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1747,23 +1746,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC6146A4-5A7B-43C5-AE78-135F431E96A0}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L102"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="4" max="4" width="23.54296875" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="14.1796875" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="11" max="11" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +1799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1839,7 +1837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1877,7 +1875,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1915,7 +1913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1953,7 +1951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1991,7 +1989,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2029,7 +2027,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -2067,7 +2065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -2105,7 +2103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2143,7 +2141,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -2181,7 +2179,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -2219,7 +2217,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -2257,7 +2255,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -2295,7 +2293,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -2333,7 +2331,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -2371,7 +2369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -2409,7 +2407,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -2447,7 +2445,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -2485,7 +2483,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2523,7 +2521,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2561,7 +2559,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -2599,7 +2597,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2637,7 +2635,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -2675,7 +2673,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -2713,7 +2711,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -2751,7 +2749,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>111</v>
       </c>
@@ -2789,7 +2787,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -2827,7 +2825,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -2865,7 +2863,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -2903,7 +2901,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -2941,7 +2939,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -2979,7 +2977,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -3017,7 +3015,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -3055,7 +3053,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -3093,7 +3091,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>163</v>
       </c>
@@ -3131,7 +3129,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>163</v>
       </c>
@@ -3169,7 +3167,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -3207,7 +3205,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>176</v>
       </c>
@@ -3245,7 +3243,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>176</v>
       </c>
@@ -3283,7 +3281,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -3321,7 +3319,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -3359,7 +3357,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>194</v>
       </c>
@@ -3397,7 +3395,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>194</v>
       </c>
@@ -3435,7 +3433,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -3473,7 +3471,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -3511,7 +3509,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -3549,7 +3547,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="48" spans="1:12" hidden="1">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>211</v>
       </c>
@@ -3587,7 +3585,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>211</v>
       </c>
@@ -3625,7 +3623,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>211</v>
       </c>
@@ -3663,7 +3661,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>211</v>
       </c>
@@ -3701,7 +3699,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>232</v>
       </c>
@@ -3739,7 +3737,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>232</v>
       </c>
@@ -3777,7 +3775,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>232</v>
       </c>
@@ -3815,7 +3813,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>245</v>
       </c>
@@ -3853,7 +3851,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>245</v>
       </c>
@@ -3891,7 +3889,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>254</v>
       </c>
@@ -3929,7 +3927,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>254</v>
       </c>
@@ -3967,7 +3965,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>254</v>
       </c>
@@ -4005,7 +4003,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>254</v>
       </c>
@@ -4043,45 +4041,45 @@
         <v>270</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="1" customFormat="1" hidden="1">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>254</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61">
         <v>2018</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>271</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" t="s">
         <v>272</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" t="s">
         <v>273</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61">
         <v>6</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I61" s="1" t="s">
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1" t="s">
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>275</v>
       </c>
@@ -4119,7 +4117,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>275</v>
       </c>
@@ -4157,7 +4155,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>275</v>
       </c>
@@ -4195,7 +4193,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>275</v>
       </c>
@@ -4233,7 +4231,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>292</v>
       </c>
@@ -4271,7 +4269,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>292</v>
       </c>
@@ -4309,7 +4307,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>292</v>
       </c>
@@ -4347,7 +4345,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>292</v>
       </c>
@@ -4385,7 +4383,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>292</v>
       </c>
@@ -4423,7 +4421,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>292</v>
       </c>
@@ -4461,7 +4459,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>292</v>
       </c>
@@ -4499,7 +4497,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>292</v>
       </c>
@@ -4537,7 +4535,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>325</v>
       </c>
@@ -4575,7 +4573,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>325</v>
       </c>
@@ -4613,7 +4611,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>334</v>
       </c>
@@ -4651,7 +4649,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>334</v>
       </c>
@@ -4689,7 +4687,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>334</v>
       </c>
@@ -4727,7 +4725,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>347</v>
       </c>
@@ -4765,7 +4763,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>347</v>
       </c>
@@ -4803,7 +4801,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>347</v>
       </c>
@@ -4841,7 +4839,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="82" spans="1:12" hidden="1">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>362</v>
       </c>
@@ -4879,7 +4877,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="83" spans="1:12" hidden="1">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>362</v>
       </c>
@@ -4917,7 +4915,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>362</v>
       </c>
@@ -4955,7 +4953,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>362</v>
       </c>
@@ -4993,7 +4991,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:12" hidden="1">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>380</v>
       </c>
@@ -5031,7 +5029,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>380</v>
       </c>
@@ -5069,7 +5067,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>389</v>
       </c>
@@ -5107,7 +5105,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>389</v>
       </c>
@@ -5145,7 +5143,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>389</v>
       </c>
@@ -5183,7 +5181,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>389</v>
       </c>
@@ -5221,7 +5219,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="92" spans="1:12" hidden="1">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>380</v>
       </c>
@@ -5259,7 +5257,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>59</v>
       </c>
@@ -5297,7 +5295,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -5335,7 +5333,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:12" hidden="1">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>176</v>
       </c>
@@ -5373,7 +5371,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>185</v>
       </c>
@@ -5411,7 +5409,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="97" spans="1:12" hidden="1">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>245</v>
       </c>
@@ -5449,7 +5447,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>275</v>
       </c>
@@ -5487,7 +5485,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>292</v>
       </c>
@@ -5525,7 +5523,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>292</v>
       </c>
@@ -5563,7 +5561,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>292</v>
       </c>
@@ -5601,7 +5599,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>325</v>
       </c>
@@ -5640,13 +5638,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L102" xr:uid="{E5AB58FF-F251-4B02-9E89-96DA0140A977}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Cameroon"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L102" xr:uid="{E5AB58FF-F251-4B02-9E89-96DA0140A977}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
